--- a/warehouse/templates/export_file/peer_pallet_template.xlsx
+++ b/warehouse/templates/export_file/peer_pallet_template.xlsx
@@ -115,6 +115,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>FBA</t>
     </r>
     <r>
@@ -130,6 +137,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>PO</t>
     </r>
     <r>
@@ -144,7 +158,7 @@
     </r>
   </si>
   <si>
-    <t>重量(kg)</t>
+    <t>重量(lbs)</t>
   </si>
   <si>
     <t>CBM</t>
@@ -366,12 +380,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -872,14 +886,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1431,27 +1445,27 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="6:7">
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+    <row r="2" customHeight="1" spans="1:13">
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
     </row>
-    <row r="3" customHeight="1" spans="6:7">
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
+    <row r="3" customHeight="1" spans="1:13">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
     </row>
-    <row r="4" customHeight="1" spans="6:7">
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+    <row r="4" customHeight="1" spans="1:13">
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
